--- a/rules/CORE-000242/negative/01/data/example-lb+send.xlsx
+++ b/rules/CORE-000242/negative/01/data/example-lb+send.xlsx
@@ -540,7 +540,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="str">
-        <v>lb.xot</v>
+        <v>lb.xpt</v>
       </c>
       <c r="C2" s="2" t="str">
         <v>Variable</v>
